--- a/sdg7臺東縣政府+我蒐集資料.xlsx
+++ b/sdg7臺東縣政府+我蒐集資料.xlsx
@@ -24,7 +24,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="78" uniqueCount="60">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="80" uniqueCount="62">
   <si>
     <t>109年</t>
   </si>
@@ -262,6 +262,14 @@
   </si>
   <si>
     <t>109-111年為臺東縣2024年縣市治民報告VLR；112-114年為自行計算 (臺東縣全年總售電量/臺東縣人口數)</t>
+    <phoneticPr fontId="2" type="noConversion"/>
+  </si>
+  <si>
+    <t>綠島鄉全年總售電量/綠島鄉抄表戶數統計</t>
+    <phoneticPr fontId="2" type="noConversion"/>
+  </si>
+  <si>
+    <t>臺東縣全年總售電量/臺東縣抄表戶數統計</t>
     <phoneticPr fontId="2" type="noConversion"/>
   </si>
 </sst>
@@ -648,11 +656,11 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
-  <dimension ref="A1:L19"/>
+  <dimension ref="A1:L21"/>
   <sheetFormatPr defaultRowHeight="15.75" x14ac:dyDescent="0.25"/>
   <cols>
     <col min="1" max="1" width="9.125" style="3" bestFit="1" customWidth="1"/>
-    <col min="2" max="2" width="33.25" style="3" bestFit="1" customWidth="1"/>
+    <col min="2" max="2" width="38.75" style="3" customWidth="1"/>
     <col min="3" max="3" width="9.125" style="3" bestFit="1" customWidth="1"/>
     <col min="4" max="4" width="9" style="3"/>
     <col min="5" max="7" width="10.75" style="3" bestFit="1" customWidth="1"/>
@@ -1369,6 +1377,76 @@
         <v>44</v>
       </c>
     </row>
+    <row r="20" spans="1:12" x14ac:dyDescent="0.25">
+      <c r="A20" s="3">
+        <v>61</v>
+      </c>
+      <c r="B20" s="2" t="s">
+        <v>61</v>
+      </c>
+      <c r="C20" s="3">
+        <v>7</v>
+      </c>
+      <c r="E20" s="3">
+        <f>E11*1000000/E14</f>
+        <v>1336.2172097272371</v>
+      </c>
+      <c r="F20" s="3">
+        <f t="shared" ref="F20:J20" si="1">F11*1000000/F14</f>
+        <v>1313.1517092748104</v>
+      </c>
+      <c r="G20" s="3">
+        <f t="shared" si="1"/>
+        <v>1332.5178146345004</v>
+      </c>
+      <c r="H20" s="3">
+        <f t="shared" si="1"/>
+        <v>1321.7481275341045</v>
+      </c>
+      <c r="I20" s="3">
+        <f t="shared" si="1"/>
+        <v>1340.4892911191957</v>
+      </c>
+      <c r="J20" s="3">
+        <f t="shared" si="1"/>
+        <v>1282.8198353550081</v>
+      </c>
+    </row>
+    <row r="21" spans="1:12" x14ac:dyDescent="0.25">
+      <c r="A21" s="3">
+        <v>62</v>
+      </c>
+      <c r="B21" s="2" t="s">
+        <v>60</v>
+      </c>
+      <c r="C21" s="3">
+        <v>7</v>
+      </c>
+      <c r="E21" s="3">
+        <f>E12/E13</f>
+        <v>1105.9682452778538</v>
+      </c>
+      <c r="F21" s="3">
+        <f t="shared" ref="F21:J21" si="2">F12/F13</f>
+        <v>1199.6376127973749</v>
+      </c>
+      <c r="G21" s="3">
+        <f t="shared" si="2"/>
+        <v>1521.4433676559661</v>
+      </c>
+      <c r="H21" s="3">
+        <f t="shared" si="2"/>
+        <v>1433.988427773344</v>
+      </c>
+      <c r="I21" s="3">
+        <f t="shared" si="2"/>
+        <v>1423.2966084687939</v>
+      </c>
+      <c r="J21" s="3">
+        <f t="shared" si="2"/>
+        <v>1296.0116858237548</v>
+      </c>
+    </row>
   </sheetData>
   <phoneticPr fontId="2" type="noConversion"/>
   <hyperlinks>
